--- a/exports/NHPC_full_report.xlsx
+++ b/exports/NHPC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.05</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>30.4</v>
+        <v>29.75</v>
       </c>
       <c r="I2" t="n">
         <v>30.27256263785</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.95</v>
+        <v>-6</v>
       </c>
       <c r="L2" t="n">
-        <v>4.11</v>
+        <v>6.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.59</v>
       </c>
       <c r="N2" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="O2" t="n">
         <v>0.64</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.49</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.38541666666</v>
+        <v>44622.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>28.1</v>
+        <v>29.4</v>
       </c>
       <c r="I3" t="n">
         <v>29.15982905875497</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>5.55</v>
+        <v>1.18</v>
       </c>
       <c r="L3" t="n">
         <v>5.71</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.34</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44677.55208333334</v>
+        <v>44678.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>33.8</v>
+        <v>32.9</v>
       </c>
       <c r="I4" t="n">
         <v>33.02376037062154</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>14.97</v>
+        <v>11.9</v>
       </c>
       <c r="L4" t="n">
         <v>7.99</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.51</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44713.38541666666</v>
+        <v>44713.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="I5" t="n">
         <v>33.8690741437084</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.13</v>
+        <v>-3.95</v>
       </c>
       <c r="L5" t="n">
         <v>5.47</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.93</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>33</v>
+        <v>31.4</v>
       </c>
       <c r="I6" t="n">
         <v>31.78803932814683</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.51</v>
+        <v>-8.19</v>
       </c>
       <c r="L6" t="n">
-        <v>5.26</v>
+        <v>8.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>4.39</v>
       </c>
       <c r="O6" t="n">
         <v>1.03</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>9.23</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>30.9</v>
+        <v>32.15</v>
       </c>
       <c r="I7" t="n">
         <v>31.43841473623845</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>1.59</v>
+        <v>-2.39</v>
       </c>
       <c r="L7" t="n">
         <v>4.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="N7" t="n">
-        <v>3.07</v>
+        <v>4.37</v>
       </c>
       <c r="O7" t="n">
         <v>-4.39</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.98</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44783.38541666666</v>
+        <v>44783.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>34.05</v>
+        <v>33.95</v>
       </c>
       <c r="I8" t="n">
         <v>34.01092388846576</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>5.91</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>5.44</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.29</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44802.38541666666</v>
+        <v>44802.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>35.4</v>
+        <v>36.1</v>
       </c>
       <c r="I9" t="n">
         <v>35.9493327468758</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.27</v>
+        <v>-6.33</v>
       </c>
       <c r="L9" t="n">
-        <v>6.04</v>
+        <v>6.77</v>
       </c>
       <c r="M9" t="n">
         <v>2.45</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44832.38541666666</v>
+        <v>44832.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="I10" t="n">
         <v>36.42472235521392</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>1.39</v>
+        <v>0.83</v>
       </c>
       <c r="L10" t="n">
         <v>1.94</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.38541666666</v>
+        <v>44838.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>37.95</v>
+        <v>38.6</v>
       </c>
       <c r="I11" t="n">
         <v>38.41700141386132</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.26</v>
+        <v>-6.04</v>
       </c>
       <c r="L11" t="n">
-        <v>4.26</v>
+        <v>6.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.41</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44867.55208333334</v>
+        <v>44868.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>41.7</v>
+        <v>41.45</v>
       </c>
       <c r="I12" t="n">
         <v>41.58076567855073</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>8.029999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="L12" t="n">
         <v>3.11</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.25</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44943.38541666666</v>
+        <v>44943.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>40.3</v>
+        <v>41.5</v>
       </c>
       <c r="I13" t="n">
         <v>40.51931028223655</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>75</v>
+        <v>75.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>2.77</v>
+        <v>-0.12</v>
       </c>
       <c r="L13" t="n">
         <v>9.050000000000001</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.56</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>41.4</v>
+        <v>40.9</v>
       </c>
       <c r="I14" t="n">
         <v>41.1706511339349</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.24</v>
+        <v>-1.45</v>
       </c>
       <c r="L14" t="n">
         <v>2.89</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44991.55208333334</v>
+        <v>44993.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>39.9</v>
+        <v>40.55</v>
       </c>
       <c r="I15" t="n">
         <v>40.49096529312484</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>2.44</v>
+        <v>0.86</v>
       </c>
       <c r="L15" t="n">
         <v>3.67</v>
@@ -1296,7 +1475,7 @@
         <v>2.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.79</v>
+        <v>4.51</v>
       </c>
       <c r="O15" t="n">
         <v>-0.6</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.25</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45013.55208333334</v>
+        <v>45014.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>39.1</v>
+        <v>38.95</v>
       </c>
       <c r="I16" t="n">
         <v>38.98125443927474</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.58</v>
+        <v>-3.95</v>
       </c>
       <c r="L16" t="n">
         <v>4.56</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.54</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>38.95</v>
+        <v>42.6</v>
       </c>
       <c r="I17" t="n">
         <v>41.10959839489782</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.16</v>
+        <v>12.32</v>
       </c>
       <c r="M17" t="n">
         <v>0.38</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.8</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>51.55</v>
+        <v>50.5</v>
       </c>
       <c r="I18" t="n">
         <v>50.78973115186292</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>205</v>
+        <v>207.8333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>21.01</v>
+        <v>18.54</v>
       </c>
       <c r="L18" t="n">
         <v>8.800000000000001</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>277</v>
+        <v>278</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.61</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>51.8</v>
+        <v>52.45</v>
       </c>
       <c r="I19" t="n">
         <v>52.34351951618104</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.57</v>
+        <v>-3.86</v>
       </c>
       <c r="L19" t="n">
         <v>4.95</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.96</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>63.95</v>
+        <v>60</v>
       </c>
       <c r="I20" t="n">
         <v>60.58624866468931</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>21.93</v>
+        <v>14.39</v>
       </c>
       <c r="L20" t="n">
         <v>1.53</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.95</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45293.38541666666</v>
+        <v>45293.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>65.5</v>
+        <v>67.95</v>
       </c>
       <c r="I21" t="n">
         <v>67.17262725109735</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.17</v>
+        <v>-13.25</v>
       </c>
       <c r="L21" t="n">
-        <v>12.42</v>
+        <v>14.58</v>
       </c>
       <c r="M21" t="n">
         <v>1.32</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.42</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>96.84999999999999</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>95.05422171978893</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>42.53</v>
+        <v>27.52</v>
       </c>
       <c r="L22" t="n">
         <v>3.61</v>
@@ -1695,7 +1958,7 @@
         <v>5.8</v>
       </c>
       <c r="N22" t="n">
-        <v>6.64</v>
+        <v>15.9</v>
       </c>
       <c r="O22" t="n">
         <v>3.11</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>24.6</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45378.38541666666</v>
+        <v>45378.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>88.63141869128718</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.33</v>
+        <v>-3.12</v>
       </c>
       <c r="L23" t="n">
         <v>14.14</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>89.65000000000001</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>88.44158455660039</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.34</v>
+        <v>-1.12</v>
       </c>
       <c r="L24" t="n">
         <v>3.3</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.15</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45411.55208333334</v>
+        <v>45412.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>93.45</v>
+        <v>94.8</v>
       </c>
       <c r="I25" t="n">
         <v>94.17604913557705</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.77</v>
+        <v>-7.3</v>
       </c>
       <c r="L25" t="n">
-        <v>6.85</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>1.6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
         <v>-2.51</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>5.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45421.38541666666</v>
+        <v>45421.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>95.8</v>
+        <v>93.7</v>
       </c>
       <c r="I26" t="n">
         <v>95.13133598459667</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>1.05</v>
+        <v>-1.16</v>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="M26" t="n">
         <v>0.91</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.27</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>97.75</v>
+        <v>102.85</v>
       </c>
       <c r="I27" t="n">
         <v>102.488659470709</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.32</v>
+        <v>-9.77</v>
       </c>
       <c r="L27" t="n">
-        <v>7.36</v>
+        <v>11.53</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.56</v>
+        <v>5.93</v>
       </c>
       <c r="O27" t="n">
         <v>-5.26</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>10.89</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>113.3</v>
+        <v>100.75</v>
       </c>
       <c r="I28" t="n">
         <v>102.7965774080999</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>10.16</v>
+        <v>-2.04</v>
       </c>
       <c r="L28" t="n">
-        <v>5.49</v>
+        <v>11.42</v>
       </c>
       <c r="M28" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.39</v>
+        <v>13.15</v>
       </c>
       <c r="O28" t="n">
         <v>5.93</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.51</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>102.96</v>
+        <v>103.55</v>
       </c>
       <c r="I29" t="n">
         <v>103.4599868212972</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.19</v>
+        <v>-2.78</v>
       </c>
       <c r="L29" t="n">
         <v>12.41</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.77</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>108.6</v>
+        <v>106.02</v>
       </c>
       <c r="I30" t="n">
         <v>106.6216293066919</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>4.88</v>
+        <v>2.39</v>
       </c>
       <c r="L30" t="n">
         <v>1.44</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45596.55208333334</v>
+        <v>45597.75</v>
       </c>
       <c r="H31" t="n">
-        <v>82.44</v>
+        <v>84.19</v>
       </c>
       <c r="I31" t="n">
         <v>83.80678555045981</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>104.1666666666667</v>
+        <v>105.3645833333333</v>
       </c>
       <c r="K31" t="n">
-        <v>22.24</v>
+        <v>20.59</v>
       </c>
       <c r="L31" t="n">
         <v>3.49</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>7.37</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>80.59999999999999</v>
+        <v>77.98</v>
       </c>
       <c r="I32" t="n">
         <v>78.94756085454577</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10.80208333333333</v>
+        <v>11.63541666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.26</v>
+        <v>-7.38</v>
       </c>
       <c r="L32" t="n">
-        <v>5.57</v>
+        <v>7.59</v>
       </c>
       <c r="M32" t="n">
         <v>3.55</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.75</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>79.05</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>82.68464586368994</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.37</v>
+        <v>-6.45</v>
       </c>
       <c r="L33" t="n">
-        <v>3.6</v>
+        <v>7.21</v>
       </c>
       <c r="M33" t="n">
-        <v>0.73</v>
+        <v>2.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>4.04</v>
       </c>
       <c r="O33" t="n">
         <v>-3.35</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.74</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>83.08</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I34" t="n">
         <v>81.98661789744952</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>0.08</v>
+        <v>-1.94</v>
       </c>
       <c r="L34" t="n">
         <v>2.63</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.23</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>77.23999999999999</v>
+        <v>78.98</v>
       </c>
       <c r="I35" t="n">
         <v>78.28939922237221</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>5.11</v>
+        <v>2.97</v>
       </c>
       <c r="L35" t="n">
         <v>3.81</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.32</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>76.98999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>75.57106916695061</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.52</v>
+        <v>-4.53</v>
       </c>
       <c r="L36" t="n">
-        <v>2.98</v>
+        <v>5.58</v>
       </c>
       <c r="M36" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>3.36</v>
       </c>
       <c r="O36" t="n">
         <v>2.05</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>6.56</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45688.38541666666</v>
+        <v>45688.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>78.48999999999999</v>
+        <v>81.25</v>
       </c>
       <c r="I37" t="n">
         <v>79.23776738100392</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.1</v>
+        <v>-7.76</v>
       </c>
       <c r="L37" t="n">
-        <v>4.64</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>0.8100000000000001</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>9.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45699.55208333334</v>
+        <v>45700.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>74.06999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="I38" t="n">
         <v>73.88413805027189</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.84</v>
+        <v>-9.43</v>
       </c>
       <c r="L38" t="n">
-        <v>9.08</v>
+        <v>12.62</v>
       </c>
       <c r="M38" t="n">
         <v>2.23</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>7.49</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>74.61</v>
+        <v>78.77</v>
       </c>
       <c r="I39" t="n">
         <v>78.41540843523823</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.39</v>
+        <v>-7.04</v>
       </c>
       <c r="L39" t="n">
-        <v>3.61</v>
+        <v>7.32</v>
       </c>
       <c r="M39" t="n">
-        <v>0.21</v>
+        <v>1.19</v>
       </c>
       <c r="N39" t="n">
-        <v>2.46</v>
+        <v>7.08</v>
       </c>
       <c r="O39" t="n">
         <v>0.2</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.66</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45713.55208333334</v>
+        <v>45715.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>76.01000000000001</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>74.38635094162254</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.5</v>
+        <v>-5.65</v>
       </c>
       <c r="L40" t="n">
-        <v>4.79</v>
+        <v>6.68</v>
       </c>
       <c r="M40" t="n">
         <v>1.28</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.77</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45733.55208333334</v>
+        <v>45734.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>78.29000000000001</v>
+        <v>79.22</v>
       </c>
       <c r="I41" t="n">
         <v>78.80564372287888</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.34</v>
+        <v>-6.59</v>
       </c>
       <c r="L41" t="n">
-        <v>6.57</v>
+        <v>6.77</v>
       </c>
       <c r="M41" t="n">
         <v>0.65</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.14</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45779.38541666666</v>
+        <v>45779.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>85.17</v>
+        <v>84.78</v>
       </c>
       <c r="I42" t="n">
         <v>85.04598314243755</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>7.51</v>
+        <v>7.02</v>
       </c>
       <c r="L42" t="n">
         <v>4.38</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.96</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45790.38541666666</v>
+        <v>45790.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59</v>
       </c>
       <c r="I43" t="n">
         <v>83.54141106847253</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="L43" t="n">
         <v>1.34</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>7.36</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>87.45</v>
+        <v>85.78</v>
       </c>
       <c r="I44" t="n">
         <v>86.79930218500201</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>4.62</v>
+        <v>2.62</v>
       </c>
       <c r="L44" t="n">
         <v>0.83</v>
       </c>
       <c r="M44" t="n">
-        <v>0.08</v>
+        <v>2.74</v>
       </c>
       <c r="N44" t="n">
         <v>2.94</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.74</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45831.38541666666</v>
+        <v>45831.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>84.14</v>
+        <v>85.5</v>
       </c>
       <c r="I45" t="n">
         <v>85.28594092278142</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>1.91</v>
+        <v>0.33</v>
       </c>
       <c r="L45" t="n">
         <v>1.35</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.4</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>86.51000000000001</v>
+        <v>85.34</v>
       </c>
       <c r="I46" t="n">
         <v>85.53345040306858</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>1.18</v>
+        <v>-0.19</v>
       </c>
       <c r="L46" t="n">
         <v>1.86</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.64</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>79.73</v>
+        <v>81.94</v>
       </c>
       <c r="I47" t="n">
         <v>80.52189195300095</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K47" t="n">
-        <v>6.57</v>
+        <v>3.98</v>
       </c>
       <c r="L47" t="n">
         <v>1.93</v>
@@ -3120,7 +3683,7 @@
         <v>1.27</v>
       </c>
       <c r="N47" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>-0.79</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.23</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>86.5</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="I48" t="n">
         <v>84.80476798186091</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>5.57</v>
+        <v>2.83</v>
       </c>
       <c r="L48" t="n">
         <v>2.59</v>
@@ -3177,7 +3752,7 @@
         <v>0.23</v>
       </c>
       <c r="N48" t="n">
-        <v>1.56</v>
+        <v>3.24</v>
       </c>
       <c r="O48" t="n">
         <v>3.1</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.83</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>76.55</v>
+        <v>77.78</v>
       </c>
       <c r="I49" t="n">
         <v>77.52025578912401</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>87</v>
       </c>
       <c r="K49" t="n">
-        <v>9.15</v>
+        <v>7.69</v>
       </c>
       <c r="L49" t="n">
         <v>4.58</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>4.5</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>80.13</v>
+        <v>79.59</v>
       </c>
       <c r="I50" t="n">
         <v>79.94852908521757</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K50" t="n">
-        <v>3.02</v>
+        <v>2.33</v>
       </c>
       <c r="L50" t="n">
         <v>1.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N50" t="n">
         <v>2.07</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.72</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>78.56</v>
+        <v>79.45</v>
       </c>
       <c r="I51" t="n">
         <v>79.41114842501231</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>1.29</v>
+        <v>0.18</v>
       </c>
       <c r="L51" t="n">
         <v>2.61</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.02</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>75.20999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="I52" t="n">
         <v>74.29782604429558</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.34</v>
+        <v>-6.61</v>
       </c>
       <c r="L52" t="n">
-        <v>6.04</v>
+        <v>6.73</v>
       </c>
       <c r="M52" t="n">
         <v>1.51</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.44</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46097.55208333334</v>
+        <v>46098.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>75.3</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>76.15668056624357</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.48</v>
+        <v>-3.19</v>
       </c>
       <c r="L53" t="n">
-        <v>3.07</v>
+        <v>3.37</v>
       </c>
       <c r="M53" t="n">
         <v>0.93</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.09</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46111.38541666666</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>74.16</v>
+        <v>73.48</v>
       </c>
       <c r="I54" t="n">
         <v>73.64028350817624</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.15</v>
+        <v>-4.04</v>
       </c>
       <c r="L54" t="n">
-        <v>3.29</v>
+        <v>4.66</v>
       </c>
       <c r="M54" t="n">
         <v>1.56</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.67</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>77.70999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I55" t="n">
         <v>78.38324911254345</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>14</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.76</v>
+        <v>-8.06</v>
       </c>
       <c r="L55" t="n">
-        <v>6.89</v>
+        <v>8.15</v>
       </c>
       <c r="M55" t="n">
         <v>3.36</v>
       </c>
       <c r="N55" t="n">
-        <v>2.3</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
         <v>-4.2</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.73</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46150.38541666666</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>81.25</v>
+        <v>80.7</v>
       </c>
       <c r="I56" t="n">
         <v>80.77545469439218</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>2.33</v>
+        <v>1.64</v>
       </c>
       <c r="L56" t="n">
         <v>1.31</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.11</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46190.55208333334</v>
+        <v>46191.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>74.44</v>
+        <v>76.33</v>
       </c>
       <c r="I57" t="n">
         <v>75.82911758573417</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>7.76</v>
+        <v>5.42</v>
       </c>
       <c r="L57" t="n">
         <v>1.23</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.43</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46230.55208333334</v>
+        <v>46231.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>79.65000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="I58" t="n">
         <v>78.23169838156308</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K58" t="n">
-        <v>4.35</v>
+        <v>2.45</v>
       </c>
       <c r="L58" t="n">
         <v>2.23</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>126</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5909,7 +6624,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.1</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="6">
@@ -5919,7 +6634,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -5929,7 +6644,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>207.8</v>
       </c>
     </row>
     <row r="8">
@@ -5939,7 +6654,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -5949,7 +6664,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -5959,7 +6674,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="11">
@@ -5969,7 +6684,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -5979,7 +6694,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -5989,7 +6704,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="14">
@@ -5999,7 +6714,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.36</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="15">
@@ -6009,7 +6724,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.21</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="16">
@@ -6019,7 +6734,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.45</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="17">
@@ -6029,7 +6744,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.53</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="18">
@@ -6039,7 +6754,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.4</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="19">
@@ -6049,7 +6764,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.5</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="20">
@@ -6059,7 +6774,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.81</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="21">
@@ -6069,7 +6784,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.14</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="22">
@@ -6079,7 +6794,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -6089,7 +6804,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6099,7 +6814,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="25">
@@ -6119,7 +6834,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.08</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="27">
@@ -6129,7 +6844,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.949999999999999</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="28">
@@ -6139,7 +6854,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
